--- a/switch_config_example.xlsx
+++ b/switch_config_example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jack Consoli\Documents\cs\scripts\brocade-rest-api-applications\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jack Consoli\Documents\cs\scripts\brocade-rest-api-applications\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDC20EA-FE60-49E4-8AD8-E18A4EE97554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E05DC2-391C-4713-AB7D-3C0109AE62B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1110" yWindow="0" windowWidth="19380" windowHeight="11520" tabRatio="664" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1485" yWindow="930" windowWidth="19005" windowHeight="10590" tabRatio="664" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example" sheetId="62" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="469">
   <si>
     <t>Port</t>
   </si>
@@ -1124,9 +1124,6 @@
     <t>Reserve</t>
   </si>
   <si>
-    <t>Typically "Yes". Applicable to fixed port switches only. Reserves a port license for the port.</t>
-  </si>
-  <si>
     <t>Fabric Principal</t>
   </si>
   <si>
@@ -1139,9 +1136,6 @@
     <t xml:space="preserve">Should be "Yes" for mainframe and AIX. Should be "No" for all else. Exceptions are for those with expert knowledge. </t>
   </si>
   <si>
-    <t>Typically "Enable". Executed after all other actions are completed.</t>
-  </si>
-  <si>
     <t>CLI commands are executed via an SSH session. Use multiple rows with "CLI" in column A or put multiple commands in the same cell on different lines. Commands are executed in the order read. Commands are processed as is. Minimal response evaluation is performed. Typically only used for long distance settings or to lock down a port as E-Port.</t>
   </si>
   <si>
@@ -1191,9 +1185,6 @@
   </si>
   <si>
     <t>PBR</t>
-  </si>
-  <si>
-    <t>Typically clear (empty cell). Usually only used for service actions. "Disable" is only executed with -force. By default, all newly added ports are disabled. When "Disable" or "Persistent Disable" is selected, that is the first action executed. "Enable" is only valid if the switch is enabled.</t>
   </si>
   <si>
     <t>Typically "Yes". Switch_x processing stops and processing of Slot x sheets begins.</t>
@@ -1415,12 +1406,6 @@
     <t>The default switch, "Switch_128", did not have insistent domain ID set. Even though the DID is not changing, setting it to insistent requires the switch to be disabled. This example shows how to disable the switch, set insistent DID, and then re-enable it. It also serves as an example on how to persistently disable ports.</t>
   </si>
   <si>
-    <t>Web Tools</t>
-  </si>
-  <si>
-    <t>Enable Web Tools (chassis management GUI without requiring SANNav). By default, Web Tools is enabled. Typically left blank for new chassis configuration.</t>
-  </si>
-  <si>
     <t>All switches using the base port will use this routing policy regardless of how the routing policy is set for the switches using the base switch, "Allow XSIL" = "Yes". It is rare, if ever, for open environments to use anything other than EBR. Other settings are generally only of concern in mainframe environments where there is a logical switch for mainframe channel connections and a seperate logical switch for peer-to-peer storage connections sharring ISLs. Keep in mind that peer-to-peer storage connection use FCP (open) protocol, not FICON. If you select EBR, make sure all channels and device connections support FiDR.</t>
   </si>
   <si>
@@ -1446,6 +1431,18 @@
   </si>
   <si>
     <t>open: No switch wide port naming. Port names may be assigned using the "Slot x" worksheets. Maximum characters: 128. ficon: Same as "open", but characters are limited to 24 characters. index: Default. The port name corresponds to the port index. fdmi: The port name corresponds to the attached FDMI host name. Do not use for FICON. dynamic: The port name corresponds to the format defined by "Port Name Format". For FICON, this field is usually either "ficon" or empty.</t>
+  </si>
+  <si>
+    <t>Applicable to fixed port switches only. Reserves a POD license for the port. A port cannot be enabled if the license has not been reserved.</t>
+  </si>
+  <si>
+    <t>Typically set. The port must be enabled to use it. Disables happen immediately. Enables will not take effect until the port is reserved, the chassis is enabled, and the switch is enabled.</t>
+  </si>
+  <si>
+    <t>Typically clear (empty cell). Intended to execute CLI commands that require the port to be disabled. By default, all newly added ports are disabled. A disable here only makes sense when reconfiguring existing enabled ports. Although "Enable" and "Persistent Disable" are available options, there is no known practical reason to use them here. Use "End Enable" for final port configuration.</t>
+  </si>
+  <si>
+    <t>Release</t>
   </si>
 </sst>
 </file>
@@ -1623,9 +1620,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1636,6 +1630,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1948,87 +1945,87 @@
   <sheetData>
     <row r="1" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -2073,7 +2070,7 @@
         <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -4844,79 +4841,79 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>307</v>
       </c>
-      <c r="B1" s="23"/>
+      <c r="B1" s="22"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="23" t="s">
         <v>325</v>
       </c>
-      <c r="B3" s="23"/>
+      <c r="B3" s="22"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>326</v>
       </c>
-      <c r="B4" s="23"/>
+      <c r="B4" s="22"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="23" t="s">
         <v>328</v>
       </c>
-      <c r="B6" s="23"/>
+      <c r="B6" s="22"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="22" t="s">
         <v>334</v>
       </c>
-      <c r="B7" s="23"/>
+      <c r="B7" s="22"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="23" t="s">
         <v>327</v>
       </c>
-      <c r="B9" s="23"/>
+      <c r="B9" s="22"/>
     </row>
     <row r="10" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="23" t="s">
-        <v>415</v>
-      </c>
-      <c r="B10" s="23"/>
+      <c r="A10" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="B10" s="22"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="23" t="s">
         <v>329</v>
       </c>
-      <c r="B12" s="23"/>
+      <c r="B12" s="22"/>
     </row>
     <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="22" t="s">
         <v>330</v>
       </c>
-      <c r="B13" s="23"/>
+      <c r="B13" s="22"/>
     </row>
     <row r="15" spans="1:2" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
-        <v>397</v>
-      </c>
-      <c r="B15" s="23"/>
+      <c r="A15" s="23" t="s">
+        <v>394</v>
+      </c>
+      <c r="B15" s="22"/>
     </row>
     <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="105" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -4926,49 +4923,49 @@
       <c r="A20" s="20"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
-        <v>372</v>
-      </c>
-      <c r="B21" s="24"/>
+      <c r="A21" s="23" t="s">
+        <v>370</v>
+      </c>
+      <c r="B21" s="23"/>
     </row>
     <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="22" t="s">
         <v>362</v>
       </c>
-      <c r="B22" s="23"/>
+      <c r="B22" s="22"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="23" t="s">
         <v>332</v>
       </c>
-      <c r="B24" s="23"/>
+      <c r="B24" s="22"/>
     </row>
     <row r="25" spans="1:2" ht="59.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="22" t="s">
         <v>331</v>
       </c>
-      <c r="B25" s="23"/>
+      <c r="B25" s="22"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="24" t="s">
+      <c r="A27" s="23" t="s">
         <v>335</v>
       </c>
-      <c r="B27" s="23"/>
+      <c r="B27" s="22"/>
     </row>
     <row r="28" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>346</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -4976,29 +4973,29 @@
         <v>336</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="B40" s="24"/>
+      <c r="A40" s="23" t="s">
+        <v>373</v>
+      </c>
+      <c r="B40" s="23"/>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
@@ -5013,7 +5010,7 @@
         <v>349</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -5045,7 +5042,7 @@
         <v>339</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -5102,7 +5099,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -5110,7 +5107,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -5134,15 +5131,15 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>387</v>
+      <c r="B15" s="26" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -5150,7 +5147,7 @@
         <v>303</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -5173,20 +5170,20 @@
         <v>311</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B27" s="26" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>364</v>
+      <c r="B29" s="26" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -5202,7 +5199,7 @@
         <v>292</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -5210,7 +5207,7 @@
         <v>305</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -5221,7 +5218,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D363350-9672-4769-A5C9-5207B1DA3378}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.42578125" style="2" customWidth="1"/>
@@ -5277,7 +5274,7 @@
         <v>313</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>314</v>
@@ -5297,10 +5294,10 @@
         <v>315</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -5322,7 +5319,7 @@
         <v>60</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -5344,31 +5341,22 @@
         <v>3</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="22" t="s">
-        <v>459</v>
-      </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="22" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>383</v>
+      <c r="C13" s="5" t="s">
+        <v>381</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="9">
+  <dataValidations count="8">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Timeout" error="TCP timeout must be an integer in the range 1-5." sqref="B11" xr:uid="{918055D0-D882-428D-B1C6-D82190480F94}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
@@ -5386,15 +5374,12 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Valid options are: Clear (empty cell), &quot;Enable&quot; or &quot;Disable&quot;." sqref="B3 B5" xr:uid="{D2335284-9F0F-4C1F-9CB0-6C83B62E7233}">
       <formula1>"Enable,Disable"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Use Yes or No only." sqref="B14" xr:uid="{10A0FEE1-2577-4FE8-9BEC-089364ED3342}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Use Yes or No only." sqref="B13" xr:uid="{10A0FEE1-2577-4FE8-9BEC-089364ED3342}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" sqref="B4" xr:uid="{0774B6C4-5149-4459-8FD0-5918227A736F}"/>
     <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Maximum rest sessions must be 1-10. Leave blank for no change. Please use pull down menu to pick an appropriate value." sqref="B12" xr:uid="{F64C13DC-CDEF-4E74-B17E-A41C37720C61}">
       <formula1>"1,2,3,4,5,6,7,8,9,10"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Value must be &quot;Enable&quot;, &quot;Disable&quot;, or blank (no change). Please use pull down menu to pick an appropriate value." sqref="B13" xr:uid="{BF984C56-7E27-48F6-A8B8-D9C0A4AD9344}">
-      <formula1>"Enable,Disable"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5444,7 +5429,7 @@
         <v>357</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>359</v>
@@ -5469,7 +5454,7 @@
         <v>21</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -5478,7 +5463,7 @@
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -5486,7 +5471,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>353</v>
@@ -5497,15 +5482,15 @@
         <v>17</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="5" t="s">
@@ -5527,7 +5512,7 @@
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="75" x14ac:dyDescent="0.25">
@@ -5535,10 +5520,10 @@
         <v>22</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -5549,7 +5534,7 @@
         <v>30</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="150" x14ac:dyDescent="0.25">
@@ -5558,7 +5543,7 @@
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="5" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -5567,7 +5552,7 @@
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="60" x14ac:dyDescent="0.25">
@@ -5576,7 +5561,7 @@
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="5" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="90" x14ac:dyDescent="0.25">
@@ -5585,7 +5570,7 @@
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="5" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -5605,7 +5590,7 @@
         <v>321</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -5625,7 +5610,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -5743,7 +5728,7 @@
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -5751,7 +5736,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>353</v>
@@ -5762,10 +5747,10 @@
         <v>17</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.25">
@@ -5792,7 +5777,7 @@
     </row>
     <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>21</v>
@@ -5820,7 +5805,7 @@
         <v>21</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -5828,10 +5813,10 @@
         <v>22</v>
       </c>
       <c r="B13" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>409</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -5842,7 +5827,7 @@
         <v>30</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="150" x14ac:dyDescent="0.25">
@@ -5850,10 +5835,10 @@
         <v>267</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -5864,7 +5849,7 @@
         <v>295</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -5875,7 +5860,7 @@
         <v>274</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -5883,10 +5868,10 @@
         <v>292</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -5894,7 +5879,7 @@
         <v>298</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>299</v>
@@ -5919,7 +5904,7 @@
         <v>321</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -5930,7 +5915,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -6042,7 +6027,7 @@
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -6050,7 +6035,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>353</v>
@@ -6061,10 +6046,10 @@
         <v>17</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.25">
@@ -6091,7 +6076,7 @@
     </row>
     <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>21</v>
@@ -6119,7 +6104,7 @@
         <v>295</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -6127,10 +6112,10 @@
         <v>22</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -6141,7 +6126,7 @@
         <v>28</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="150" x14ac:dyDescent="0.25">
@@ -6149,10 +6134,10 @@
         <v>267</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -6163,7 +6148,7 @@
         <v>21</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="60" x14ac:dyDescent="0.25">
@@ -6174,7 +6159,7 @@
         <v>274</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -6185,7 +6170,7 @@
         <v>28</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -6205,7 +6190,7 @@
         <v>295</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="21" spans="1:3" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -6216,29 +6201,29 @@
         <v>321</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>463</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -6249,7 +6234,7 @@
         <v>21</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -6354,7 +6339,7 @@
         <v>357</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>359</v>
@@ -6366,7 +6351,7 @@
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -6374,7 +6359,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>353</v>
@@ -6385,10 +6370,10 @@
         <v>17</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.25">
@@ -6415,13 +6400,13 @@
     </row>
     <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>295</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -6430,7 +6415,7 @@
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="5" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -6439,7 +6424,7 @@
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="5" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -6447,10 +6432,10 @@
         <v>22</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -6461,7 +6446,7 @@
         <v>26</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="60" x14ac:dyDescent="0.25">
@@ -6469,10 +6454,10 @@
         <v>267</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -6483,7 +6468,7 @@
         <v>295</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="120" x14ac:dyDescent="0.25">
@@ -6494,7 +6479,7 @@
         <v>274</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -6505,7 +6490,7 @@
         <v>30</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -6514,7 +6499,7 @@
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="5" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -6523,7 +6508,7 @@
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="5" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="21" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6534,7 +6519,7 @@
         <v>321</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -6545,7 +6530,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -6618,32 +6603,32 @@
     <col min="3" max="5" width="5.85546875" style="12" customWidth="1"/>
     <col min="6" max="6" width="6.85546875" style="12" customWidth="1"/>
     <col min="7" max="7" width="4.5703125" style="13" customWidth="1"/>
-    <col min="8" max="8" width="17.7109375" style="13" customWidth="1"/>
+    <col min="8" max="8" width="8.7109375" style="13" customWidth="1"/>
     <col min="9" max="9" width="40" style="14" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" style="13" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="13" customWidth="1"/>
     <col min="11" max="11" width="8.7109375" style="13" customWidth="1"/>
     <col min="12" max="13" width="20.7109375" style="14" customWidth="1"/>
     <col min="14" max="16" width="4.85546875" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="24" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
     </row>
     <row r="2" spans="2:16" s="1" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="B2" s="11" t="s">
@@ -9342,13 +9327,13 @@
         <f t="shared" ref="G68:G128" si="13">G69</f>
         <v>128</v>
       </c>
-      <c r="H68" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H68" s="17"/>
       <c r="I68" s="18"/>
-      <c r="J68" s="17"/>
+      <c r="J68" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K68" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L68" s="18"/>
       <c r="M68" s="18"/>
@@ -9390,13 +9375,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H69" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H69" s="17"/>
       <c r="I69" s="18"/>
-      <c r="J69" s="17"/>
+      <c r="J69" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K69" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L69" s="18"/>
       <c r="M69" s="18"/>
@@ -9438,13 +9423,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H70" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H70" s="17"/>
       <c r="I70" s="18"/>
-      <c r="J70" s="17"/>
+      <c r="J70" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K70" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L70" s="18"/>
       <c r="M70" s="18"/>
@@ -9486,13 +9471,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H71" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H71" s="17"/>
       <c r="I71" s="18"/>
-      <c r="J71" s="17"/>
+      <c r="J71" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K71" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L71" s="18"/>
       <c r="M71" s="18"/>
@@ -9534,13 +9519,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H72" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H72" s="17"/>
       <c r="I72" s="18"/>
-      <c r="J72" s="17"/>
+      <c r="J72" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K72" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L72" s="18"/>
       <c r="M72" s="18"/>
@@ -9582,13 +9567,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H73" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H73" s="17"/>
       <c r="I73" s="18"/>
-      <c r="J73" s="17"/>
+      <c r="J73" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K73" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L73" s="18"/>
       <c r="M73" s="18"/>
@@ -9630,13 +9615,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H74" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H74" s="17"/>
       <c r="I74" s="18"/>
-      <c r="J74" s="17"/>
+      <c r="J74" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K74" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L74" s="18"/>
       <c r="M74" s="18"/>
@@ -9678,13 +9663,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H75" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H75" s="17"/>
       <c r="I75" s="18"/>
-      <c r="J75" s="17"/>
+      <c r="J75" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K75" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L75" s="18"/>
       <c r="M75" s="18"/>
@@ -9726,13 +9711,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H76" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H76" s="17"/>
       <c r="I76" s="18"/>
-      <c r="J76" s="17"/>
+      <c r="J76" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K76" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L76" s="18"/>
       <c r="M76" s="18"/>
@@ -9774,13 +9759,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H77" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H77" s="17"/>
       <c r="I77" s="18"/>
-      <c r="J77" s="17"/>
+      <c r="J77" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K77" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L77" s="18"/>
       <c r="M77" s="18"/>
@@ -9822,13 +9807,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H78" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H78" s="17"/>
       <c r="I78" s="18"/>
-      <c r="J78" s="17"/>
+      <c r="J78" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K78" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L78" s="18"/>
       <c r="M78" s="18"/>
@@ -9870,13 +9855,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H79" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H79" s="17"/>
       <c r="I79" s="18"/>
-      <c r="J79" s="17"/>
+      <c r="J79" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K79" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L79" s="18"/>
       <c r="M79" s="18"/>
@@ -9918,13 +9903,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H80" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H80" s="17"/>
       <c r="I80" s="18"/>
-      <c r="J80" s="17"/>
+      <c r="J80" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K80" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L80" s="18"/>
       <c r="M80" s="18"/>
@@ -9966,13 +9951,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H81" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H81" s="17"/>
       <c r="I81" s="18"/>
-      <c r="J81" s="17"/>
+      <c r="J81" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K81" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L81" s="18"/>
       <c r="M81" s="18"/>
@@ -10014,13 +9999,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H82" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H82" s="17"/>
       <c r="I82" s="18"/>
-      <c r="J82" s="17"/>
+      <c r="J82" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K82" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L82" s="18"/>
       <c r="M82" s="18"/>
@@ -10062,13 +10047,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H83" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H83" s="17"/>
       <c r="I83" s="18"/>
-      <c r="J83" s="17"/>
+      <c r="J83" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K83" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L83" s="18"/>
       <c r="M83" s="18"/>
@@ -10110,13 +10095,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H84" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H84" s="17"/>
       <c r="I84" s="18"/>
-      <c r="J84" s="17"/>
+      <c r="J84" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K84" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L84" s="18"/>
       <c r="M84" s="18"/>
@@ -10158,13 +10143,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H85" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H85" s="17"/>
       <c r="I85" s="18"/>
-      <c r="J85" s="17"/>
+      <c r="J85" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K85" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L85" s="18"/>
       <c r="M85" s="18"/>
@@ -10206,13 +10191,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H86" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H86" s="17"/>
       <c r="I86" s="18"/>
-      <c r="J86" s="17"/>
+      <c r="J86" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K86" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L86" s="18"/>
       <c r="M86" s="18"/>
@@ -10254,13 +10239,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H87" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H87" s="17"/>
       <c r="I87" s="18"/>
-      <c r="J87" s="17"/>
+      <c r="J87" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K87" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L87" s="18"/>
       <c r="M87" s="18"/>
@@ -10302,13 +10287,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H88" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H88" s="17"/>
       <c r="I88" s="18"/>
-      <c r="J88" s="17"/>
+      <c r="J88" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K88" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L88" s="18"/>
       <c r="M88" s="18"/>
@@ -10350,13 +10335,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H89" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H89" s="17"/>
       <c r="I89" s="18"/>
-      <c r="J89" s="17"/>
+      <c r="J89" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K89" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L89" s="18"/>
       <c r="M89" s="18"/>
@@ -10398,13 +10383,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H90" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H90" s="17"/>
       <c r="I90" s="18"/>
-      <c r="J90" s="17"/>
+      <c r="J90" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K90" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L90" s="18"/>
       <c r="M90" s="18"/>
@@ -10446,13 +10431,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H91" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H91" s="17"/>
       <c r="I91" s="18"/>
-      <c r="J91" s="17"/>
+      <c r="J91" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K91" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L91" s="18"/>
       <c r="M91" s="18"/>
@@ -10494,13 +10479,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H92" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H92" s="17"/>
       <c r="I92" s="18"/>
-      <c r="J92" s="17"/>
+      <c r="J92" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K92" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L92" s="18"/>
       <c r="M92" s="18"/>
@@ -10542,13 +10527,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H93" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H93" s="17"/>
       <c r="I93" s="18"/>
-      <c r="J93" s="17"/>
+      <c r="J93" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K93" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L93" s="18"/>
       <c r="M93" s="18"/>
@@ -10590,13 +10575,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H94" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H94" s="17"/>
       <c r="I94" s="18"/>
-      <c r="J94" s="17"/>
+      <c r="J94" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K94" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L94" s="18"/>
       <c r="M94" s="18"/>
@@ -10638,13 +10623,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H95" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H95" s="17"/>
       <c r="I95" s="18"/>
-      <c r="J95" s="17"/>
+      <c r="J95" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K95" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L95" s="18"/>
       <c r="M95" s="18"/>
@@ -10686,13 +10671,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H96" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H96" s="17"/>
       <c r="I96" s="18"/>
-      <c r="J96" s="17"/>
+      <c r="J96" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K96" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L96" s="18"/>
       <c r="M96" s="18"/>
@@ -10734,13 +10719,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H97" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H97" s="17"/>
       <c r="I97" s="18"/>
-      <c r="J97" s="17"/>
+      <c r="J97" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K97" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L97" s="18"/>
       <c r="M97" s="18"/>
@@ -10782,13 +10767,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H98" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H98" s="17"/>
       <c r="I98" s="18"/>
-      <c r="J98" s="17"/>
+      <c r="J98" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K98" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L98" s="18"/>
       <c r="M98" s="18"/>
@@ -10830,13 +10815,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H99" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H99" s="17"/>
       <c r="I99" s="18"/>
-      <c r="J99" s="17"/>
+      <c r="J99" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K99" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L99" s="18"/>
       <c r="M99" s="18"/>
@@ -10878,13 +10863,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H100" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H100" s="17"/>
       <c r="I100" s="18"/>
-      <c r="J100" s="17"/>
+      <c r="J100" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K100" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L100" s="18"/>
       <c r="M100" s="18"/>
@@ -10926,13 +10911,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H101" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H101" s="17"/>
       <c r="I101" s="18"/>
-      <c r="J101" s="17"/>
+      <c r="J101" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K101" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L101" s="18"/>
       <c r="M101" s="18"/>
@@ -10974,13 +10959,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H102" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H102" s="17"/>
       <c r="I102" s="18"/>
-      <c r="J102" s="17"/>
+      <c r="J102" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K102" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L102" s="18"/>
       <c r="M102" s="18"/>
@@ -11022,13 +11007,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H103" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H103" s="17"/>
       <c r="I103" s="18"/>
-      <c r="J103" s="17"/>
+      <c r="J103" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K103" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L103" s="18"/>
       <c r="M103" s="18"/>
@@ -11070,13 +11055,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H104" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H104" s="17"/>
       <c r="I104" s="18"/>
-      <c r="J104" s="17"/>
+      <c r="J104" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K104" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L104" s="18"/>
       <c r="M104" s="18"/>
@@ -11118,13 +11103,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H105" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H105" s="17"/>
       <c r="I105" s="18"/>
-      <c r="J105" s="17"/>
+      <c r="J105" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K105" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L105" s="18"/>
       <c r="M105" s="18"/>
@@ -11166,13 +11151,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H106" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H106" s="17"/>
       <c r="I106" s="18"/>
-      <c r="J106" s="17"/>
+      <c r="J106" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K106" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L106" s="18"/>
       <c r="M106" s="18"/>
@@ -11214,13 +11199,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H107" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H107" s="17"/>
       <c r="I107" s="18"/>
-      <c r="J107" s="17"/>
+      <c r="J107" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K107" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L107" s="18"/>
       <c r="M107" s="18"/>
@@ -11262,13 +11247,13 @@
         <f t="shared" si="13"/>
         <v>128</v>
       </c>
-      <c r="H108" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H108" s="17"/>
       <c r="I108" s="18"/>
-      <c r="J108" s="17"/>
+      <c r="J108" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K108" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L108" s="18"/>
       <c r="M108" s="18"/>
@@ -11310,13 +11295,13 @@
         <f>Switch_128!B3</f>
         <v>128</v>
       </c>
-      <c r="H109" s="17" t="s">
-        <v>392</v>
-      </c>
+      <c r="H109" s="17"/>
       <c r="I109" s="18"/>
-      <c r="J109" s="17"/>
+      <c r="J109" s="17" t="s">
+        <v>389</v>
+      </c>
       <c r="K109" s="16" t="s">
-        <v>295</v>
+        <v>468</v>
       </c>
       <c r="L109" s="18"/>
       <c r="M109" s="18"/>
@@ -11364,7 +11349,7 @@
         <v>321</v>
       </c>
       <c r="K110" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L110" s="18"/>
       <c r="M110" s="18" t="str">
@@ -11415,7 +11400,7 @@
         <v>321</v>
       </c>
       <c r="K111" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L111" s="18"/>
       <c r="M111" s="18" t="str">
@@ -11466,7 +11451,7 @@
         <v>321</v>
       </c>
       <c r="K112" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L112" s="18"/>
       <c r="M112" s="18" t="str">
@@ -11517,7 +11502,7 @@
         <v>321</v>
       </c>
       <c r="K113" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L113" s="18"/>
       <c r="M113" s="18" t="str">
@@ -11568,7 +11553,7 @@
         <v>321</v>
       </c>
       <c r="K114" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L114" s="18"/>
       <c r="M114" s="18" t="str">
@@ -11619,7 +11604,7 @@
         <v>321</v>
       </c>
       <c r="K115" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L115" s="18"/>
       <c r="M115" s="18" t="str">
@@ -11670,7 +11655,7 @@
         <v>321</v>
       </c>
       <c r="K116" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L116" s="18"/>
       <c r="M116" s="18" t="str">
@@ -11721,7 +11706,7 @@
         <v>321</v>
       </c>
       <c r="K117" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L117" s="18"/>
       <c r="M117" s="18" t="str">
@@ -11772,7 +11757,7 @@
         <v>321</v>
       </c>
       <c r="K118" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L118" s="18"/>
       <c r="M118" s="18" t="str">
@@ -11823,7 +11808,7 @@
         <v>321</v>
       </c>
       <c r="K119" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L119" s="18"/>
       <c r="M119" s="18" t="str">
@@ -11874,7 +11859,7 @@
         <v>321</v>
       </c>
       <c r="K120" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L120" s="18"/>
       <c r="M120" s="18" t="str">
@@ -11925,7 +11910,7 @@
         <v>321</v>
       </c>
       <c r="K121" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L121" s="18"/>
       <c r="M121" s="18" t="str">
@@ -11976,7 +11961,7 @@
         <v>321</v>
       </c>
       <c r="K122" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L122" s="18"/>
       <c r="M122" s="18"/>
@@ -12024,7 +12009,7 @@
         <v>321</v>
       </c>
       <c r="K123" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L123" s="18"/>
       <c r="M123" s="18"/>
@@ -12072,7 +12057,7 @@
         <v>321</v>
       </c>
       <c r="K124" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L124" s="18"/>
       <c r="M124" s="18"/>
@@ -12120,7 +12105,7 @@
         <v>321</v>
       </c>
       <c r="K125" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L125" s="18"/>
       <c r="M125" s="18"/>
@@ -12168,7 +12153,7 @@
         <v>321</v>
       </c>
       <c r="K126" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L126" s="18"/>
       <c r="M126" s="18"/>
@@ -12216,7 +12201,7 @@
         <v>321</v>
       </c>
       <c r="K127" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L127" s="18"/>
       <c r="M127" s="18"/>
@@ -12264,7 +12249,7 @@
         <v>321</v>
       </c>
       <c r="K128" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L128" s="18"/>
       <c r="M128" s="18"/>
@@ -12312,7 +12297,7 @@
         <v>321</v>
       </c>
       <c r="K129" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L129" s="18"/>
       <c r="M129" s="18"/>
@@ -12354,15 +12339,17 @@
         <f>G131</f>
         <v>30</v>
       </c>
-      <c r="H130" s="17"/>
+      <c r="H130" s="17" t="s">
+        <v>400</v>
+      </c>
       <c r="I130" s="19" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="J130" s="17" t="s">
         <v>321</v>
       </c>
       <c r="K130" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L130" s="18"/>
       <c r="M130" s="18" t="str">
@@ -12405,15 +12392,17 @@
         <f>Switch_base!B3</f>
         <v>30</v>
       </c>
-      <c r="H131" s="17"/>
+      <c r="H131" s="17" t="s">
+        <v>400</v>
+      </c>
       <c r="I131" s="19" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="J131" s="17" t="s">
         <v>321</v>
       </c>
       <c r="K131" s="16" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="L131" s="18"/>
       <c r="M131" s="18" t="str">
@@ -12438,11 +12427,11 @@
     <mergeCell ref="B1:P1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Valid options are: Clear (empty cell), &quot;Yes&quot; or &quot;No&quot;." sqref="K4:K131" xr:uid="{9B44BE40-F0F1-4C81-B97F-45C5B3081D5F}">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Valid options are: Clear (empty cell), &quot;Enable&quot;, &quot;Disable&quot;, or Persistent Disable." sqref="H4:H131 J4:J131" xr:uid="{3E5B968C-23B0-47C4-A3D5-E1C44706FD47}">
       <formula1>"Enable,Disable,Persistent Disable"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Valid options are: Clear (empty cell), &quot;Yes&quot; or &quot;No&quot;." sqref="K4:K131" xr:uid="{D244EFC8-DCEF-473F-88C2-1C8DBF2A2B84}">
+      <formula1>"Reserve,Release"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
